--- a/Vizitky/Vizitky_raw.xlsx
+++ b/Vizitky/Vizitky_raw.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/petrchaloupek/HelmacKonference/Vizitky/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC88F08F-2D95-D240-8823-7D24BBD94F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{127999C2-755A-D646-BCBA-4DB28D940CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17160" xr2:uid="{7EC535FB-41E3-7D4C-8503-9411C42E6B9C}"/>
   </bookViews>
@@ -1160,22 +1160,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="110" name="Obrázek 109">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A28F2016-DD63-3C48-AC64-A3180DAE2929}"/>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="111" name="Obrázek 110">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A1F8043-28B3-0345-BBC8-5BFF0D82AB64}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1185,56 +1185,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="152400" y="7467600"/>
-          <a:ext cx="3200400" cy="1828800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="111" name="Obrázek 110">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A1F8043-28B3-0345-BBC8-5BFF0D82AB64}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1284,7 +1234,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1334,7 +1284,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId24" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1384,7 +1334,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1434,7 +1384,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1484,7 +1434,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1534,7 +1484,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1584,7 +1534,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1634,7 +1584,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1684,7 +1634,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1715,8 +1665,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>3206104</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5704</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>1827017</xdr:rowOff>
     </xdr:to>
@@ -1734,7 +1684,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId32" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1765,8 +1715,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>3206104</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>5704</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -1784,7 +1734,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId34" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId33" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1815,8 +1765,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>3206104</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5704</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -1834,7 +1784,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId34" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1865,8 +1815,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>3204678</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>4278</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -1884,7 +1834,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId35" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1915,8 +1865,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>3206104</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>5704</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -1934,7 +1884,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId37" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId36" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1965,8 +1915,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>3206104</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5704</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
@@ -1984,7 +1934,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId37" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2015,8 +1965,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>3206104</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>5704</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
@@ -2034,7 +1984,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId39" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId38" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2065,8 +2015,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>3206104</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>5704</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
@@ -2084,7 +2034,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId40" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId39" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2115,8 +2065,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>3206104</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5704</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -2134,7 +2084,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId41" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId40" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2165,8 +2115,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>3206104</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>5704</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -2184,7 +2134,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId42" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId41" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2215,8 +2165,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>3206104</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>5704</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -2234,7 +2184,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId43" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId42" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2265,8 +2215,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>3206104</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5704</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
@@ -2284,7 +2234,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId44" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId43" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2315,8 +2265,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>3206104</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>5704</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
@@ -2334,7 +2284,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId45" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId44" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2365,8 +2315,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>3206104</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>5704</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -2384,7 +2334,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId45" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2409,66 +2359,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>3204678</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>-1</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="137" name="Obrázek 136">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04390E2C-7841-6B43-8E98-A398FE31736C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3208421" y="27405263"/>
-          <a:ext cx="3204678" cy="1827017"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>4278</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>3204678</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>-1</xdr:rowOff>
+      <xdr:rowOff>1828799</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2484,7 +2384,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2515,8 +2415,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>3204678</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>4278</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -2534,7 +2434,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2565,8 +2465,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>3204678</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>4278</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -2584,7 +2484,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2615,8 +2515,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>3204678</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>4278</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -2634,7 +2534,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2665,10 +2565,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>3204678</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>-1</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>4278</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>1828799</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2684,7 +2584,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2715,10 +2615,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>3204678</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>-1</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>4278</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>1828799</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2734,7 +2634,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2765,10 +2665,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>3204678</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>-1</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>4278</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>1828799</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2784,7 +2684,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2815,8 +2715,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>3204678</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>4278</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -2834,7 +2734,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2865,8 +2765,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>3204678</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>4278</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -2884,7 +2784,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2915,8 +2815,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>3204678</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>4278</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -2934,7 +2834,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2965,10 +2865,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>3204678</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>-1</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>4278</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1828799</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2984,7 +2884,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3015,10 +2915,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>3204678</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>-1</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>4278</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1828799</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3034,7 +2934,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3065,10 +2965,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>3204678</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>-1</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>4278</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1828799</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3084,7 +2984,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3115,8 +3015,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>3204678</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>4278</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -3134,7 +3034,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3165,8 +3065,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>3204678</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>4278</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -3184,7 +3084,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3215,8 +3115,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>3204678</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>4278</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -3234,7 +3134,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId46" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -3265,8 +3165,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>3200400</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>1782</xdr:rowOff>
     </xdr:to>
@@ -3284,6 +3184,56 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="27405263"/>
+          <a:ext cx="3200400" cy="1828800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Obrázek 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10E56DBE-FAF5-8948-AE03-8694BE23C0DA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId48" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
@@ -3297,7 +3247,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="27405263"/>
+          <a:off x="3200400" y="27432000"/>
           <a:ext cx="3200400" cy="1828800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
